--- a/reports/2026-10-26_report.xlsx
+++ b/reports/2026-10-26_report.xlsx
@@ -602,22 +602,22 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>0.4817338844670522</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>0.309092968949944</v>
+        <v>0.3114351718778278</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.1726409155171082</v>
+        <v>0.1702987125892244</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.5174617360712146</v>
+        <v>0.503009719537203</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>6.01</v>
+        <v>5.87</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -666,26 +666,26 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>LeoVegas (SE)</t>
+          <t>BetOnline.ag</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>0.2732293280606688</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.1320004203084973</v>
+        <v>0.1262279603047906</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.1412289077521715</v>
+        <v>0.1470013677558782</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1.18583462448535</v>
+        <v>1.322449288515685</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>6.01</v>
+        <v>5.87</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -812,10 +812,10 @@
         <v>0.5663856491891375</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.4316891196306048</v>
+        <v>0.4334780299427436</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.1346965295585327</v>
+        <v>0.1329076192463938</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0.3083508496269076</v>
@@ -880,10 +880,10 @@
         <v>0.4052558735534644</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2960505967785158</v>
+        <v>0.2971815334764055</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1092052767749486</v>
+        <v>0.108074340077059</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0.3292392652553633</v>
@@ -1016,10 +1016,10 @@
         <v>0.5126615246731944</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4357270184528076</v>
+        <v>0.4379013177444689</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.07693450622038678</v>
+        <v>0.07476020692872543</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0.1534884305146873</v>
@@ -1152,10 +1152,10 @@
         <v>0.3281719697433276</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2654955338393907</v>
+        <v>0.2654960836574638</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06267643590393684</v>
+        <v>0.06267588608586377</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0.201109409260579</v>
@@ -1278,26 +1278,26 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>LeoVegas (SE)</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.8</v>
+        <v>5.97</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.2289512239889124</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1707653027709504</v>
+        <v>0.1681909812418258</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.05818592121796201</v>
+        <v>0.06076024274708655</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3279170991356917</v>
+        <v>0.3668388072138069</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>5.13</v>
+        <v>5.41</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
@@ -1468,25 +1468,25 @@
         <v>0.7212557462215556</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.7026224299265937</v>
+        <v>0.7017340943332945</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.0186333162949619</v>
+        <v>0.01952165188826116</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>20</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>0.06612256618029419</v>
+        <v>0.06515087810749827</v>
       </c>
     </row>
     <row r="3">
@@ -1531,7 +1531,7 @@
         <v>0.1706540893486733</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1890711290894552</v>
+        <v>0.1898561652916934</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>5.4</v>
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="N3" s="6" t="n">
-        <v>-0.01841703974078188</v>
+        <v>-0.01920207594302012</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>20</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.06612256618029419</v>
+        <v>0.06515087810749827</v>
       </c>
     </row>
     <row r="4">
@@ -1594,7 +1594,7 @@
         <v>0.1080901644297713</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1083064409839511</v>
+        <v>0.1084097403750121</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>10.5</v>
@@ -1605,14 +1605,14 @@
         </is>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-0.0002162765541798423</v>
+        <v>-0.0003195759452408048</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>20</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>0.06612256618029419</v>
+        <v>0.06515087810749827</v>
       </c>
     </row>
     <row r="5">
@@ -1657,7 +1657,7 @@
         <v>0.4336143508108625</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.5683108803693951</v>
+        <v>0.5665219700572564</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>1.72</v>
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="N5" s="6" t="n">
-        <v>-0.1346965295585327</v>
+        <v>-0.1329076192463939</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>13</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.06418217802956956</v>
+        <v>0.06423645227553068</v>
       </c>
     </row>
     <row r="6">
@@ -1720,7 +1720,7 @@
         <v>0.5663856491891375</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.4316891196306048</v>
+        <v>0.4334780299427436</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>2.31</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1346965295585327</v>
+        <v>0.1329076192463938</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.06418217802956956</v>
+        <v>0.06423645227553068</v>
       </c>
     </row>
     <row r="7">
@@ -1787,7 +1787,7 @@
         <v>0.297037277774192</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.289194620931399</v>
+        <v>0.2894556968596319</v>
       </c>
       <c r="L7" s="5" t="n">
         <v>3.5</v>
@@ -1798,14 +1798,14 @@
         </is>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.007842656842793061</v>
+        <v>0.007581580914560127</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>20</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>0.06539676139664863</v>
+        <v>0.06584922898588053</v>
       </c>
     </row>
     <row r="8">
@@ -1850,10 +1850,10 @@
         <v>0.246092538457281</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.2666961022585951</v>
+        <v>0.267869342813336</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1861,14 +1861,14 @@
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>-0.02060356380131409</v>
+        <v>-0.02177680435605503</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>20</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>0.06539676139664863</v>
+        <v>0.06584922898588053</v>
       </c>
     </row>
     <row r="9">
@@ -1913,7 +1913,7 @@
         <v>0.4568701837685269</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.4441092768100059</v>
+        <v>0.442674960327032</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>2.24</v>
@@ -1924,14 +1924,14 @@
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.012760906958521</v>
+        <v>0.01419522344149493</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>20</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.06539676139664863</v>
+        <v>0.06584922898588053</v>
       </c>
     </row>
     <row r="10">
@@ -1976,7 +1976,7 @@
         <v>0.4873384753268056</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.5642729815471924</v>
+        <v>0.5620986822555311</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>1.76</v>
@@ -1987,14 +1987,14 @@
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-0.07693450622038678</v>
+        <v>-0.07476020692872543</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>13</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0.06288242836888425</v>
+        <v>0.06302303297815952</v>
       </c>
     </row>
     <row r="11">
@@ -2039,7 +2039,7 @@
         <v>0.5126615246731944</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4357270184528076</v>
+        <v>0.4379013177444689</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>2.25</v>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.07693450622038678</v>
+        <v>0.07476020692872543</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>13</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.06288242836888425</v>
+        <v>0.06302303297815952</v>
       </c>
     </row>
     <row r="12">
@@ -3063,10 +3063,10 @@
         <v>0.4978194479504187</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.6972342769205524</v>
+        <v>0.7055810584533836</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -3074,14 +3074,14 @@
         </is>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.1994148289701337</v>
+        <v>-0.2077616105029649</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
         <v>20</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.06065939127144528</v>
+        <v>0.05901501524910461</v>
       </c>
     </row>
     <row r="28">
@@ -3126,18 +3126,18 @@
         <v>0.2289512239889124</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1707653027709504</v>
+        <v>0.1681909812418258</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>5.8</v>
+        <v>5.97</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>LeoVegas (SE)</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.05818592121796201</v>
+        <v>0.06076024274708655</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>20</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.06065939127144528</v>
+        <v>0.05901501524910461</v>
       </c>
     </row>
     <row r="29">
@@ -3193,18 +3193,18 @@
         <v>0.2732293280606688</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1320004203084973</v>
+        <v>0.1262279603047906</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>LeoVegas (SE)</t>
+          <t>BetOnline.ag</t>
         </is>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1412289077521715</v>
+        <v>0.1470013677558782</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>20</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.06065939127144528</v>
+        <v>0.05901501524910461</v>
       </c>
     </row>
     <row r="30">
@@ -3260,10 +3260,10 @@
         <v>0.5182661155329478</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.690907031050056</v>
+        <v>0.6885648281221721</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -3271,14 +3271,14 @@
         </is>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.1726409155171083</v>
+        <v>-0.1702987125892244</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
         <v>3</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0.06179459714063062</v>
+        <v>0.06281172521075711</v>
       </c>
     </row>
     <row r="31">
@@ -3323,10 +3323,10 @@
         <v>0.4817338844670522</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.309092968949944</v>
+        <v>0.3114351718778278</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1726409155171082</v>
+        <v>0.1702987125892244</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>3</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.06179459714063062</v>
+        <v>0.06281172521075711</v>
       </c>
     </row>
     <row r="32">
@@ -3390,25 +3390,25 @@
         <v>0.4735166036365016</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.4649179409330951</v>
+        <v>0.4661349466760776</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.008598662703406534</v>
+        <v>0.007381656960424032</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>0.08004351333007996</v>
+        <v>0.0826766878024074</v>
       </c>
     </row>
     <row r="33">
@@ -3453,25 +3453,25 @@
         <v>0.2172606794730085</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.2433545209469138</v>
+        <v>0.2431515753544185</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.02609384147390531</v>
+        <v>-0.02589089588141005</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0.08004351333007996</v>
+        <v>0.0826766878024074</v>
       </c>
     </row>
     <row r="34">
@@ -3516,25 +3516,25 @@
         <v>0.3092227168904899</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.2917275381199912</v>
+        <v>0.290713477969504</v>
       </c>
       <c r="L34" s="5" t="n">
         <v>3.4</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>BetOnline.ag</t>
+          <t>Tipico</t>
         </is>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01749517877049872</v>
+        <v>0.01850923892098594</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>0.08004351333007996</v>
+        <v>0.0826766878024074</v>
       </c>
     </row>
     <row r="35">
@@ -3579,7 +3579,7 @@
         <v>0.4180459248078948</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.4673814752624971</v>
+        <v>0.4654043294717943</v>
       </c>
       <c r="L35" s="5" t="n">
         <v>2.05</v>
@@ -3590,14 +3590,14 @@
         </is>
       </c>
       <c r="N35" s="6" t="n">
-        <v>-0.04933555045460236</v>
+        <v>-0.04735840466389957</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
         <v>16</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>0.09081607149254592</v>
+        <v>0.09081375048838668</v>
       </c>
     </row>
     <row r="36">
@@ -3642,7 +3642,7 @@
         <v>0.2537821054487779</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.2671229908981121</v>
+        <v>0.2690995868707419</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>3.6</v>
@@ -3653,14 +3653,14 @@
         </is>
       </c>
       <c r="N36" s="6" t="n">
-        <v>-0.01334088544933421</v>
+        <v>-0.01531748142196399</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
         <v>16</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>0.09081607149254592</v>
+        <v>0.09081375048838668</v>
       </c>
     </row>
     <row r="37">
@@ -3705,7 +3705,7 @@
         <v>0.3281719697433276</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.2654955338393907</v>
+        <v>0.2654960836574638</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>3.66</v>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.06267643590393684</v>
+        <v>0.06267588608586377</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>16</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>0.09081607149254592</v>
+        <v>0.09081375048838668</v>
       </c>
     </row>
     <row r="38">
@@ -3965,7 +3965,7 @@
         <v>0.4052558735534644</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0.2960505967785158</v>
+        <v>0.2971815334764055</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>3.28</v>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.1092052767749486</v>
+        <v>0.108074340077059</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>16</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>0.09188338222927919</v>
+        <v>0.09209120760859847</v>
       </c>
     </row>
     <row r="42">
@@ -4032,7 +4032,7 @@
         <v>0.2305694635045024</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.2564404292743606</v>
+        <v>0.2568207595034283</v>
       </c>
       <c r="L42" s="5" t="n">
         <v>3.85</v>
@@ -4043,14 +4043,14 @@
         </is>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.0258709657698582</v>
+        <v>-0.02625129599892589</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>16</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>0.09188338222927919</v>
+        <v>0.09209120760859847</v>
       </c>
     </row>
     <row r="43">
@@ -4095,7 +4095,7 @@
         <v>0.3641746629420332</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.4475089739471236</v>
+        <v>0.4459977070201663</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>2.12</v>
@@ -4106,14 +4106,14 @@
         </is>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.08333431100509048</v>
+        <v>-0.08182304407813312</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
         <v>16</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>0.09188338222927919</v>
+        <v>0.09209120760859847</v>
       </c>
     </row>
     <row r="44">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 10:16 CAT</t>
+          <t>2026-10-26 11:01 CAT</t>
         </is>
       </c>
     </row>

--- a/reports/2026-10-26_report.xlsx
+++ b/reports/2026-10-26_report.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -605,19 +605,19 @@
         <v>3.12</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.4817338844670522</v>
+        <v>0.4817342476936864</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>0.3114351718778278</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.1702987125892244</v>
+        <v>0.1702990758158586</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.503009719537203</v>
+        <v>0.5030108528043018</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>5.87</v>
+        <v>5.48</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
@@ -673,19 +673,19 @@
         <v>8.5</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.2732293280606688</v>
+        <v>0.27322970308262</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>0.1262279603047906</v>
+        <v>0.1249319681946774</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.1470013677558782</v>
+        <v>0.1482977348879426</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1.322449288515685</v>
+        <v>1.32245247620227</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>5.87</v>
+        <v>5.48</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -741,19 +741,19 @@
         <v>1.36</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.8505899431101326</v>
+        <v>0.8505888634301765</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>0.7121150068384903</v>
+        <v>0.7118036295576755</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.1384749362716423</v>
+        <v>0.138785233872501</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.1568023226297803</v>
+        <v>0.1568008542650401</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>8.57</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -809,19 +809,19 @@
         <v>2.31</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.5663856491891375</v>
+        <v>0.566398349661079</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>0.4334780299427436</v>
+        <v>0.4279816801706033</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.1329076192463938</v>
+        <v>0.1384166694904758</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0.3083508496269076</v>
+        <v>0.3083801877170926</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>11.43</v>
+        <v>10.81</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
@@ -877,19 +877,19 @@
         <v>3.28</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.4052558735534644</v>
+        <v>0.4052558678447982</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2971815334764055</v>
+        <v>0.2960505967785158</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.108074340077059</v>
+        <v>0.1092052710662824</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3292392652553633</v>
+        <v>0.3292392465309379</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>11.43</v>
+        <v>10.81</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
@@ -942,22 +942,22 @@
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.7948951870129631</v>
+        <v>0.7948878913789159</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.7162327650764283</v>
+        <v>0.7129420827455455</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.07866242193653483</v>
+        <v>0.08194580863337042</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.0572105987272411</v>
+        <v>0.06514977444774739</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>8.57</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
         <v>2.25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.5126615246731944</v>
+        <v>0.5126663032410721</v>
       </c>
       <c r="L8" s="4" t="n">
         <v>0.4379013177444689</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.07476020692872543</v>
+        <v>0.07476498549660315</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1534884305146873</v>
+        <v>0.1534991822924123</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>11.43</v>
+        <v>10.81</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -1044,60 +1044,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>celtic</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>dundee united</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Match result (1X2)</t>
+          <t>Over/Under 2.5 goals</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Home (1)</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1xBet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.8010752281583394</v>
+        <v>0.539354477935249</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.7381676101281736</v>
+        <v>0.4750334619048814</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.06290761803016587</v>
+        <v>0.06432101603036766</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.01736553976109101</v>
+        <v>0.1056766797672604</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>9.19</v>
+        <v>8.48</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
         </is>
       </c>
     </row>
@@ -1149,19 +1149,19 @@
         <v>3.66</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3281719697433276</v>
+        <v>0.3281720332757039</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2654960836574638</v>
+        <v>0.2654955338393907</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06267588608586377</v>
+        <v>0.06267649943631315</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.201109409260579</v>
+        <v>0.2011096417890763</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>10.8</v>
+        <v>10.22</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1180,56 +1180,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>celtic</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>dundee united</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Over/Under 2.5 goals</t>
+          <t>Match result (1X2)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Home (1)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>2.02</v>
+        <v>1.27</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.539347754085523</v>
+        <v>0.8010751765401429</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4776734213867465</v>
+        <v>0.7389739225448702</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.06167433269877659</v>
+        <v>0.06210125399527278</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.08948246325275666</v>
+        <v>0.01736547420598145</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>11.43</v>
+        <v>8.69</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -1282,26 +1282,94 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.97</v>
+        <v>6.07</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2289512239889124</v>
+        <v>0.2289504072035201</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.1681909812418258</v>
+        <v>0.1669678114830033</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.06076024274708655</v>
+        <v>0.06198259572051684</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3668388072138069</v>
+        <v>0.3897289717253671</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>5.41</v>
+        <v>5.27</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
           <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap; already published by an earlier run (original pick kept - never duplicated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Italy Serie A</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Match result (1X2)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Away (2)</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Unibet (SE)</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.2249462101208006</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0.1736096074948679</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0.05133660262593265</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0.3721718817368833</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>second source: unavailable (plan_scope) (recorded, not substituted); stake scaled down: correlated same-fixture exposure cap; stake scaled down: total-exposure cap</t>
         </is>
       </c>
     </row>
@@ -1465,28 +1533,28 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0.7212557462215556</v>
+        <v>0.7212440040216547</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>0.7017340943332945</v>
+        <v>0.7070076254033165</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Unibet (SE)</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N2" s="6" t="n">
-        <v>0.01952165188826116</v>
+        <v>0.01423637861833815</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>20</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>0.06515087810749827</v>
+        <v>0.06469045508467217</v>
       </c>
     </row>
     <row r="3">
@@ -1528,28 +1596,28 @@
         </is>
       </c>
       <c r="J3" s="6" t="n">
-        <v>0.1706540893486733</v>
+        <v>0.1706615811807623</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>0.1898561652916934</v>
+        <v>0.1868168105238613</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Winamax (DE)</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N3" s="6" t="n">
-        <v>-0.01920207594302012</v>
+        <v>-0.01615522934309901</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>20</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>0.06515087810749827</v>
+        <v>0.06469045508467217</v>
       </c>
     </row>
     <row r="4">
@@ -1591,10 +1659,10 @@
         </is>
       </c>
       <c r="J4" s="6" t="n">
-        <v>0.1080901644297713</v>
+        <v>0.108094414797583</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>0.1084097403750121</v>
+        <v>0.1061755640728221</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>10.5</v>
@@ -1605,14 +1673,14 @@
         </is>
       </c>
       <c r="N4" s="6" t="n">
-        <v>-0.0003195759452408048</v>
+        <v>0.001918850724760876</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>20</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>0.06515087810749827</v>
+        <v>0.06469045508467217</v>
       </c>
     </row>
     <row r="5">
@@ -1654,13 +1722,13 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>0.4336143508108625</v>
+        <v>0.433601650338921</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>0.5665219700572564</v>
+        <v>0.5720183198293968</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1668,14 +1736,14 @@
         </is>
       </c>
       <c r="N5" s="6" t="n">
-        <v>-0.1329076192463939</v>
+        <v>-0.1384166694904758</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>13</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>0.06423645227553068</v>
+        <v>0.06362499773512481</v>
       </c>
     </row>
     <row r="6">
@@ -1717,10 +1785,10 @@
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.5663856491891375</v>
+        <v>0.566398349661079</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.4334780299427436</v>
+        <v>0.4279816801706033</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>2.31</v>
@@ -1731,7 +1799,7 @@
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1329076192463938</v>
+        <v>0.1384166694904758</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -1742,7 +1810,7 @@
         <v>13</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.06423645227553068</v>
+        <v>0.06362499773512481</v>
       </c>
     </row>
     <row r="7">
@@ -1784,28 +1852,28 @@
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.297037277774192</v>
+        <v>0.2970342458292495</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>0.2894556968596319</v>
+        <v>0.2898741546227411</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Betsson</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.007581580914560127</v>
+        <v>0.007160091206508457</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>20</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>0.06584922898588053</v>
+        <v>0.06572088978819089</v>
       </c>
     </row>
     <row r="8">
@@ -1847,10 +1915,10 @@
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.246092538457281</v>
+        <v>0.2460950796224059</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.267869342813336</v>
+        <v>0.2679773709759602</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>3.7</v>
@@ -1861,14 +1929,14 @@
         </is>
       </c>
       <c r="N8" s="6" t="n">
-        <v>-0.02177680435605503</v>
+        <v>-0.02188229135355427</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>20</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>0.06584922898588053</v>
+        <v>0.06572088978819089</v>
       </c>
     </row>
     <row r="9">
@@ -1910,10 +1978,10 @@
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.4568701837685269</v>
+        <v>0.4568706745483447</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.442674960327032</v>
+        <v>0.4421484744012988</v>
       </c>
       <c r="L9" s="5" t="n">
         <v>2.24</v>
@@ -1924,14 +1992,14 @@
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.01419522344149493</v>
+        <v>0.01472220014704595</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>20</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0.06584922898588053</v>
+        <v>0.06572088978819089</v>
       </c>
     </row>
     <row r="10">
@@ -1973,7 +2041,7 @@
         </is>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.4873384753268056</v>
+        <v>0.4873336967589278</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0.5620986822555311</v>
@@ -1987,7 +2055,7 @@
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>-0.07476020692872543</v>
+        <v>-0.07476498549660321</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
@@ -2036,7 +2104,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.5126615246731944</v>
+        <v>0.5126663032410721</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0.4379013177444689</v>
@@ -2050,7 +2118,7 @@
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.07476020692872543</v>
+        <v>0.07476498549660315</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -2103,10 +2171,10 @@
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.5549001043938652</v>
+        <v>0.5549007159132419</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>0.5854517555461004</v>
+        <v>0.5896391413643582</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>1.69</v>
@@ -2117,14 +2185,14 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>-0.03055165115223524</v>
+        <v>-0.03473842545111638</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>20</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>0.06525280426230841</v>
+        <v>0.06601017129151716</v>
       </c>
     </row>
     <row r="13">
@@ -2166,10 +2234,10 @@
         </is>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.2201504219192593</v>
+        <v>0.2201530739659575</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>0.2383190317815684</v>
+        <v>0.2367512511407738</v>
       </c>
       <c r="L13" s="5" t="n">
         <v>4.2</v>
@@ -2180,77 +2248,81 @@
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>-0.01816860986230903</v>
+        <v>-0.01659817717481629</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>20</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>0.06525280426230841</v>
+        <v>0.06601017129151716</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Italy Serie A</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>ac milan v bologna</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="3" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Match result (1X2)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Away (2)</t>
         </is>
       </c>
-      <c r="J14" s="6" t="n">
-        <v>0.2249494736868754</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>0.1762292126723313</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Tipico</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>0.04872026101454413</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="n">
+      <c r="J14" s="4" t="n">
+        <v>0.2249462101208006</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.1736096074948679</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Unibet (SE)</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0.05133660262593265</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v>0.06525280426230841</v>
+      <c r="Q14" s="4" t="n">
+        <v>0.06601017129151716</v>
       </c>
     </row>
     <row r="15">
@@ -2292,10 +2364,10 @@
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.460652245914477</v>
+        <v>0.4606455220647509</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.5223265786132535</v>
+        <v>0.5249665380951186</v>
       </c>
       <c r="L15" s="5" t="n">
         <v>1.93</v>
@@ -2306,14 +2378,14 @@
         </is>
       </c>
       <c r="N15" s="6" t="n">
-        <v>-0.06167433269877654</v>
+        <v>-0.06432101603036772</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>15</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.05859410236049054</v>
+        <v>0.05819951337251027</v>
       </c>
     </row>
     <row r="16">
@@ -2355,21 +2427,21 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.539347754085523</v>
+        <v>0.539354477935249</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4776734213867465</v>
+        <v>0.4750334619048814</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>Unibet (SE)</t>
         </is>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.06167433269877659</v>
+        <v>0.06432101603036766</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -2380,7 +2452,7 @@
         <v>15</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.05859410236049054</v>
+        <v>0.05819951337251027</v>
       </c>
     </row>
     <row r="17">
@@ -2422,10 +2494,10 @@
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.2219055504308327</v>
+        <v>0.2219056698312021</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.1773476292693122</v>
+        <v>0.177184903915884</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>5.75</v>
@@ -2436,14 +2508,14 @@
         </is>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.04455792116152046</v>
+        <v>0.04472076591531809</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>20</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0.06564427827805672</v>
+        <v>0.06537435185733456</v>
       </c>
     </row>
     <row r="18">
@@ -2485,10 +2557,10 @@
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.2349942527928667</v>
+        <v>0.2349984539552127</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0.2529459830720209</v>
+        <v>0.252992023423391</v>
       </c>
       <c r="L18" s="5" t="n">
         <v>4.01</v>
@@ -2499,14 +2571,14 @@
         </is>
       </c>
       <c r="N18" s="6" t="n">
-        <v>-0.01795173027915414</v>
+        <v>-0.01799356946817832</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>20</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>0.06564427827805672</v>
+        <v>0.06537435185733456</v>
       </c>
     </row>
     <row r="19">
@@ -2548,10 +2620,10 @@
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.5431001967763008</v>
+        <v>0.5430958762135852</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>0.5697063876586669</v>
+        <v>0.569823072660725</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>1.7</v>
@@ -2562,14 +2634,14 @@
         </is>
       </c>
       <c r="N19" s="6" t="n">
-        <v>-0.02660619088236604</v>
+        <v>-0.02672719644713972</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>20</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>0.06564427827805672</v>
+        <v>0.06537435185733456</v>
       </c>
     </row>
     <row r="20">
@@ -2611,7 +2683,7 @@
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.4158589943174056</v>
+        <v>0.4158500075094176</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0.4600488250569849</v>
@@ -2625,7 +2697,7 @@
         </is>
       </c>
       <c r="N20" s="6" t="n">
-        <v>-0.04418983073957933</v>
+        <v>-0.04419881754756733</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
@@ -2674,7 +2746,7 @@
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5841410056825944</v>
+        <v>0.5841499924905824</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0.5399511749430151</v>
@@ -2688,7 +2760,7 @@
         </is>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.04418983073957927</v>
+        <v>0.04419881754756727</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
@@ -2737,10 +2809,10 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.06594443814396483</v>
+        <v>0.06594408883469993</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1209782333260216</v>
+        <v>0.1215906493351021</v>
       </c>
       <c r="L22" s="5" t="n">
         <v>9</v>
@@ -2751,14 +2823,14 @@
         </is>
       </c>
       <c r="N22" s="6" t="n">
-        <v>-0.05503379518205674</v>
+        <v>-0.05564656050040213</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>20</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>0.06704463248472753</v>
+        <v>0.06628705237975627</v>
       </c>
     </row>
     <row r="23">
@@ -2800,10 +2872,10 @@
         </is>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.08346561874590247</v>
+        <v>0.08346704773512341</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.1669067598354881</v>
+        <v>0.1666057211072224</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>6.11</v>
@@ -2814,14 +2886,14 @@
         </is>
       </c>
       <c r="N23" s="6" t="n">
-        <v>-0.08344114108958564</v>
+        <v>-0.08313867337209903</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>20</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>0.06704463248472753</v>
+        <v>0.06628705237975627</v>
       </c>
     </row>
     <row r="24">
@@ -2863,10 +2935,10 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8505899431101326</v>
+        <v>0.8505888634301765</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7121150068384903</v>
+        <v>0.7118036295576755</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>1.36</v>
@@ -2877,7 +2949,7 @@
         </is>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1384749362716423</v>
+        <v>0.138785233872501</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -2888,7 +2960,7 @@
         <v>20</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.06704463248472753</v>
+        <v>0.06628705237975627</v>
       </c>
     </row>
     <row r="25">
@@ -2930,13 +3002,13 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.7948951870129631</v>
+        <v>0.7948878913789159</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.7162327650764283</v>
+        <v>0.7129420827455455</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2944,7 +3016,7 @@
         </is>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.07866242193653483</v>
+        <v>0.08194580863337042</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -2955,7 +3027,7 @@
         <v>3</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.06049424571992112</v>
+        <v>0.06007217984776517</v>
       </c>
     </row>
     <row r="26">
@@ -2997,13 +3069,13 @@
         </is>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.2051048129870369</v>
+        <v>0.2051121086210841</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.2837672349235716</v>
+        <v>0.2870579172544545</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>3.37</v>
+        <v>3.31</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -3011,14 +3083,14 @@
         </is>
       </c>
       <c r="N26" s="6" t="n">
-        <v>-0.07866242193653478</v>
+        <v>-0.08194580863337037</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>3</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0.06049424571992112</v>
+        <v>0.06007217984776517</v>
       </c>
     </row>
     <row r="27">
@@ -3060,10 +3132,10 @@
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.4978194479504187</v>
+        <v>0.49781988971386</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.7055810584533836</v>
+        <v>0.7081002203223193</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>1.38</v>
@@ -3074,14 +3146,14 @@
         </is>
       </c>
       <c r="N27" s="6" t="n">
-        <v>-0.2077616105029649</v>
+        <v>-0.2102803306084593</v>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
         <v>20</v>
       </c>
       <c r="Q27" s="6" t="n">
-        <v>0.05901501524910461</v>
+        <v>0.05886372101837047</v>
       </c>
     </row>
     <row r="28">
@@ -3123,13 +3195,13 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2289512239889124</v>
+        <v>0.2289504072035201</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1681909812418258</v>
+        <v>0.1669678114830033</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>5.97</v>
+        <v>6.07</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -3137,7 +3209,7 @@
         </is>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.06076024274708655</v>
+        <v>0.06198259572051684</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -3148,7 +3220,7 @@
         <v>20</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.05901501524910461</v>
+        <v>0.05886372101837047</v>
       </c>
     </row>
     <row r="29">
@@ -3190,10 +3262,10 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2732293280606688</v>
+        <v>0.27322970308262</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1262279603047906</v>
+        <v>0.1249319681946774</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>8.5</v>
@@ -3204,7 +3276,7 @@
         </is>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.1470013677558782</v>
+        <v>0.1482977348879426</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -3215,7 +3287,7 @@
         <v>20</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.05901501524910461</v>
+        <v>0.05886372101837047</v>
       </c>
     </row>
     <row r="30">
@@ -3257,7 +3329,7 @@
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.5182661155329478</v>
+        <v>0.5182657523063136</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0.6885648281221721</v>
@@ -3271,7 +3343,7 @@
         </is>
       </c>
       <c r="N30" s="6" t="n">
-        <v>-0.1702987125892244</v>
+        <v>-0.1702990758158586</v>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
@@ -3320,7 +3392,7 @@
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.4817338844670522</v>
+        <v>0.4817342476936864</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>0.3114351718778278</v>
@@ -3334,7 +3406,7 @@
         </is>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.1702987125892244</v>
+        <v>0.1702990758158586</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -3387,28 +3459,28 @@
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.4735166036365016</v>
+        <v>0.4735168328110065</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.4661349466760776</v>
+        <v>0.4675588916188824</v>
       </c>
       <c r="L32" s="5" t="n">
         <v>2.08</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Coolbet</t>
+          <t>1xBet</t>
         </is>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.007381656960424032</v>
+        <v>0.005957941192124172</v>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>0.0826766878024074</v>
+        <v>0.08090492169520877</v>
       </c>
     </row>
     <row r="33">
@@ -3450,28 +3522,28 @@
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.2172606794730085</v>
+        <v>0.2172606400520705</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.2431515753544185</v>
+        <v>0.2442266947193628</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Coolbet</t>
         </is>
       </c>
       <c r="N33" s="6" t="n">
-        <v>-0.02589089588141005</v>
+        <v>-0.02696605466729232</v>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q33" s="6" t="n">
-        <v>0.0826766878024074</v>
+        <v>0.08090492169520877</v>
       </c>
     </row>
     <row r="34">
@@ -3513,28 +3585,28 @@
         </is>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.3092227168904899</v>
+        <v>0.309222527136923</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.290713477969504</v>
+        <v>0.2882144136617548</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Tipico</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01850923892098594</v>
+        <v>0.02100811347516823</v>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q34" s="6" t="n">
-        <v>0.0826766878024074</v>
+        <v>0.08090492169520877</v>
       </c>
     </row>
     <row r="35">
@@ -3576,10 +3648,10 @@
         </is>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.4180459248078948</v>
+        <v>0.418045870892002</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.4654043294717943</v>
+        <v>0.4673814752624971</v>
       </c>
       <c r="L35" s="5" t="n">
         <v>2.05</v>
@@ -3590,14 +3662,14 @@
         </is>
       </c>
       <c r="N35" s="6" t="n">
-        <v>-0.04735840466389957</v>
+        <v>-0.04933560437049511</v>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
         <v>16</v>
       </c>
       <c r="Q35" s="6" t="n">
-        <v>0.09081375048838668</v>
+        <v>0.09081607149254592</v>
       </c>
     </row>
     <row r="36">
@@ -3639,10 +3711,10 @@
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.2537821054487779</v>
+        <v>0.2537820958322941</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>0.2690995868707419</v>
+        <v>0.2671229908981121</v>
       </c>
       <c r="L36" s="5" t="n">
         <v>3.6</v>
@@ -3653,14 +3725,14 @@
         </is>
       </c>
       <c r="N36" s="6" t="n">
-        <v>-0.01531748142196399</v>
+        <v>-0.01334089506581798</v>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
         <v>16</v>
       </c>
       <c r="Q36" s="6" t="n">
-        <v>0.09081375048838668</v>
+        <v>0.09081607149254592</v>
       </c>
     </row>
     <row r="37">
@@ -3702,10 +3774,10 @@
         </is>
       </c>
       <c r="J37" s="4" t="n">
-        <v>0.3281719697433276</v>
+        <v>0.3281720332757039</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.2654960836574638</v>
+        <v>0.2654955338393907</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>3.66</v>
@@ -3716,7 +3788,7 @@
         </is>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.06267588608586377</v>
+        <v>0.06267649943631315</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -3727,7 +3799,7 @@
         <v>16</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>0.09081375048838668</v>
+        <v>0.09081607149254592</v>
       </c>
     </row>
     <row r="38">
@@ -3769,10 +3841,10 @@
         </is>
       </c>
       <c r="J38" s="4" t="n">
-        <v>0.8010752281583394</v>
+        <v>0.8010751765401429</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.7381676101281736</v>
+        <v>0.7389739225448702</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>1.27</v>
@@ -3783,7 +3855,7 @@
         </is>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.06290761803016587</v>
+        <v>0.06210125399527278</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -3794,7 +3866,7 @@
         <v>16</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>0.08916895324523232</v>
+        <v>0.08910314680456315</v>
       </c>
     </row>
     <row r="39">
@@ -3836,10 +3908,10 @@
         </is>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.1140551896587242</v>
+        <v>0.1140551984525676</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.1602476919598013</v>
+        <v>0.1601489731653121</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>6.5</v>
@@ -3850,14 +3922,14 @@
         </is>
       </c>
       <c r="N39" s="6" t="n">
-        <v>-0.04619250230107706</v>
+        <v>-0.04609377471274455</v>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
         <v>16</v>
       </c>
       <c r="Q39" s="6" t="n">
-        <v>0.08916895324523232</v>
+        <v>0.08910314680456315</v>
       </c>
     </row>
     <row r="40">
@@ -3899,13 +3971,13 @@
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>0.08486958218293643</v>
+        <v>0.08486962500728958</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.1015846979120252</v>
+        <v>0.1008771042898177</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>10.1</v>
+        <v>10.27</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3913,14 +3985,14 @@
         </is>
       </c>
       <c r="N40" s="6" t="n">
-        <v>-0.01671511572908875</v>
+        <v>-0.01600747928252812</v>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>16</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>0.08916895324523232</v>
+        <v>0.08910314680456315</v>
       </c>
     </row>
     <row r="41">
@@ -3962,10 +4034,10 @@
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>0.4052558735534644</v>
+        <v>0.4052558678447982</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0.2971815334764055</v>
+        <v>0.2960505967785158</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>3.28</v>
@@ -3976,7 +4048,7 @@
         </is>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.108074340077059</v>
+        <v>0.1092052710662824</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -3987,7 +4059,7 @@
         <v>16</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>0.09209120760859847</v>
+        <v>0.09188338222927919</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4101,10 @@
         </is>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0.2305694635045024</v>
+        <v>0.2305694342025552</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>0.2568207595034283</v>
+        <v>0.2564404292743606</v>
       </c>
       <c r="L42" s="5" t="n">
         <v>3.85</v>
@@ -4043,14 +4115,14 @@
         </is>
       </c>
       <c r="N42" s="6" t="n">
-        <v>-0.02625129599892589</v>
+        <v>-0.02587099507180535</v>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>16</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>0.09209120760859847</v>
+        <v>0.09188338222927919</v>
       </c>
     </row>
     <row r="43">
@@ -4092,10 +4164,10 @@
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>0.3641746629420332</v>
+        <v>0.3641746979526467</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>0.4459977070201663</v>
+        <v>0.4475089739471236</v>
       </c>
       <c r="L43" s="5" t="n">
         <v>2.12</v>
@@ -4106,14 +4178,14 @@
         </is>
       </c>
       <c r="N43" s="6" t="n">
-        <v>-0.08182304407813312</v>
+        <v>-0.0833342759944769</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
         <v>16</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>0.09209120760859847</v>
+        <v>0.09188338222927919</v>
       </c>
     </row>
     <row r="44">
@@ -4155,10 +4227,10 @@
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0.2789756190212063</v>
+        <v>0.2789756290932971</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>0.2821947244249661</v>
+        <v>0.2839186063268248</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>3.4</v>
@@ -4169,14 +4241,14 @@
         </is>
       </c>
       <c r="N44" s="6" t="n">
-        <v>-0.003219105403759748</v>
+        <v>-0.004942977233527657</v>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
         <v>16</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>0.0912149896001596</v>
+        <v>0.0912133141830286</v>
       </c>
     </row>
     <row r="45">
@@ -4218,10 +4290,10 @@
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0.2535196518023775</v>
+        <v>0.25351965651166</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>0.2582758657050602</v>
+        <v>0.258276251077695</v>
       </c>
       <c r="L45" s="5" t="n">
         <v>3.85</v>
@@ -4232,14 +4304,14 @@
         </is>
       </c>
       <c r="N45" s="6" t="n">
-        <v>-0.004756213902682771</v>
+        <v>-0.004756594566035</v>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
         <v>16</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>0.0912149896001596</v>
+        <v>0.0912133141830286</v>
       </c>
     </row>
     <row r="46">
@@ -4281,10 +4353,10 @@
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0.4675047291764162</v>
+        <v>0.467504714395043</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>0.4595294098699737</v>
+        <v>0.4578051425954802</v>
       </c>
       <c r="L46" s="5" t="n">
         <v>2.08</v>
@@ -4295,14 +4367,14 @@
         </is>
       </c>
       <c r="N46" s="6" t="n">
-        <v>0.007975319306442463</v>
+        <v>0.009699571799562878</v>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
         <v>16</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>0.0912149896001596</v>
+        <v>0.0912133141830286</v>
       </c>
     </row>
   </sheetData>
@@ -4344,7 +4416,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26 11:01 CAT</t>
+          <t>2026-10-26 12:23 CAT</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4453,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -4391,7 +4463,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="8">
